--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4749" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5056" uniqueCount="612">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2024-06-24</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -492,7 +492,11 @@
 </t>
   </si>
   <si>
-    <t>当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。例えば、実施日に連番を付加した番号など。</t>
+    <t>Observationのためのビジネス識別子  
+【JP Core仕様】当該口腔診査（検査項目）に対して、施設内で割り振られる一意の識別子。</t>
+  </si>
+  <si>
+    <t>例：実施日に連番を付加した番号</t>
   </si>
   <si>
     <t>観測を区別し、参照することを可能にします。 / Allows observations to be distinguished and referenced.</t>
@@ -521,7 +525,10 @@
 </t>
   </si>
   <si>
-    <t>未使用</t>
+    <t>実施されるプラン、提案、依頼  【JP Core仕様】未使用</t>
+  </si>
+  <si>
+    <t>本プロファイル（特定の歯の有無・状態）は口腔診査レポートに紐付く前提のため、本プロファイル特有の定義はしない。</t>
   </si>
   <si>
     <t>イベントの許可を追跡し、提案/勧告が行われたかどうかを追跡することができます。 / Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -547,6 +554,9 @@
 </t>
   </si>
   <si>
+    <t>参照されるイベントの一部分 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>ObservationをEncounterにencounter要素を使ってリンクする。もうひとつ別のObservationを参照することについては、以降にあるt [Notes](observation.html#obsgrouping)　をガイダンスとして参照のこと。</t>
   </si>
   <si>
@@ -562,7 +572,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>結果の状態</t>
+    <t>結果の状態 【JP Core仕様】ステータス</t>
   </si>
   <si>
     <t>このリソースは現在有効でないというマークをするコードを含んでいるため、この要素はモディファイアー（修飾的要素）として位置づけられている。</t>
@@ -605,13 +615,13 @@
 </t>
   </si>
   <si>
-    <t>このObservationを分類するコード</t>
-  </si>
-  <si>
-    <t>3つのコードを設定する。
-第1コード（first）は、simpleObservationコード体系を必須とし、procedureを設定する。
-第2コード（second）は、歯科を表すコードLP89803-8を設定する。
-第3コード（third）は、歯の有無や処置状態などを表すコードを設定する。なお、日本では適切なコード体系が存在しないため、独自のバリューセットを定義する。</t>
+    <t>Observationの種類（タイプ）の分類</t>
+  </si>
+  <si>
+    <t>JP Core仕様】以下を指定する。  
+第1コード：exam  
+第2コード：LP89803-8 （Dental）  
+第3コード：DO-1-02 （ToothTreatmentCondition）</t>
   </si>
   <si>
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
@@ -804,7 +814,7 @@
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
-    <t>procedure</t>
+    <t>exam</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -829,9 +839,6 @@
   </si>
   <si>
     <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Procedure</t>
   </si>
   <si>
     <t>Coding.display</t>
@@ -1055,7 +1062,8 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>このObservationの対象を特定するコード。LOINCより歯の有無・状態を表す54570-7を選択する。</t>
+    <t>observation のタイプ（コードまたはタイプ）
+【JP Core仕様】54570-7（Oral/dental status）を指定する</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
@@ -1095,7 +1103,7 @@
 </t>
   </si>
   <si>
-    <t>患者情報</t>
+    <t>観察対象者 【JP Core仕様】患者情報</t>
   </si>
   <si>
     <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
@@ -1123,6 +1131,9 @@
 </t>
   </si>
   <si>
+    <t>subject 要素が実際のobservationの対象でない場合に、observation の対象物。【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>T通常、observationは対象（患者、または患者のグループ、場所、またはデバイス）について行われ、対象とobservationのために直接測定されるものとの区別は、observationコード自体（例：「血糖値」 ）で記述され、この要素を使用して個別に表す必要はない。検体（標本）への参照が必要な場合は、 `specimen`要素を使用する。リソースの代わりにコードが必要な場合は、人体部位には`bodysite`要素を使用するか、標準の拡張機能[focusCode]（extension-observation-focuscode.html）を使用する。</t>
   </si>
   <si>
@@ -1140,10 +1151,10 @@
 </t>
   </si>
   <si>
+    <t>このobservationが行われるヘルスケアイベント</t>
+  </si>
+  <si>
     <t>例：診療、歯科健診（検診）、身元不明者調査</t>
-  </si>
-  <si>
-    <t>通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
   </si>
   <si>
     <t>一部の観察では、観察と特定のEncounterの間のリンクを知ることが重要かもしれません。 / For some observations it may be important to know the link between an observation and a particular encounter.</t>
@@ -1172,7 +1183,7 @@
 </t>
   </si>
   <si>
-    <t>実施日時</t>
+    <t>臨床的に関連する時刻または時間 【JP Core仕様】実施日時</t>
   </si>
   <si>
     <t>この観察結果が過去の報告でない限り、少なくとも日付が存在する必要がある。不正確または「あいまいな」時間を記録するには（たとえば、「朝食後」に行われた血糖測定）、[Timing]（datatypes.html＃timing）データ型を使用して、測定を通常のライフイベントに関連付けることができる。</t>
@@ -1200,7 +1211,7 @@
 </t>
   </si>
   <si>
-    <t>所見確定日時</t>
+    <t>このバージョンが利用可能となった日時 【JP Core仕様】所見確定日時</t>
   </si>
   <si>
     <t>レビューと検証を必要としないobservationの場合、リソース自体の[`lastUpdated`]（resource-definitions.html＃Meta.lastUpdated）日時と同じになる場合がある。特定の更新のレビューと検証が必要なobservationの場合、新しいバージョンを再度レビューして検証する必要がないような臨床的に重要でない更新がなされたために、リソース自体の「lastUpdated」時間はこれと異なる場合がある。</t>
@@ -1222,12 +1233,12 @@
 </t>
   </si>
   <si>
+    <t>observationに責任をもつ者</t>
+  </si>
+  <si>
     <t>例：歯科医師など</t>
   </si>
   <si>
-    <t>参照は、実際のFHIRリソースへの参照である必要があり、解決可能（内容に到達可能）である必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
-  </si>
-  <si>
     <t>観察にある程度の自信を与える可能性があり、また、フォローアップの質問をどこに向けるべきかを示します。 / May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
@@ -1246,10 +1257,10 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>使用しない</t>
-  </si>
-  <si>
-    <t>日本仕様ではComponent要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない。</t>
+    <t>実際の結果値 【JP Core仕様】component要素を利用して複数の結果を表現することを考慮しているため、本要素は使用しない</t>
+  </si>
+  <si>
+    <t>観察にはあります。1）ここでの単一の値、2）関連する値とコンポーネント値のセット、または3）関連またはコンポーネント値のセットのみ。値が存在する場合、この要素のデータ型は、viscervation.codeによって決定する必要があります。フィールドが通常コーディングされている場合、または観測に関連付けられたタイプの場合、文字列の代わりにテキストのみを持つCodeableconecteが使用されます。コードはコード化された値を定義します。追加のガイダンスについては、以下の[[メモ]セクション]（[観察.html＃注）を参照してください。 / An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1274,7 +1285,7 @@
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
-    <t>結果が存在しなかった場合、その理由</t>
+    <t>結結果が欠損値である理由 【JP Core仕様】結果が存在しなかった場合、その理由</t>
   </si>
   <si>
     <t>ヌル値または例外値は、FHIRオブザベーションで2つの方法で表すことができる。 1つの方法は、それらを値セットに含めて、値の例外を表す方法である。たとえば、血清学的検査の測定値は、「検出された」、「検出されなかった」、「決定的でない」、または「検体が不十分」である可能性がある。別の方法は、実際の観測にvalue要素を使用し、明示的なdataAbsentReason要素を使用して例外的な値を記録することである。たとえば、測定が完了しなかった場合、dataAbsentReasonコード「error」を使用できる。この場合には、観測値は、報告する値がある場合にのみ報告される可能性があることに注意する必要がある。たとえば、差分セルカウント値は&gt; 0の場合にのみ報告される場合がある。これらのオプションのため、nullまたは例外値の一般的な観測値を解釈するにはユースケースの合意が必要である。</t>
@@ -1286,7 +1297,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1306,6 +1317,9 @@
 </t>
   </si>
   <si>
+    <t>高、低、正常等の結果のカテゴリ分けした評価 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>「異常フラグ」として呼ばれる検査結果解釈コードが従来から使用されており、その使用はコード化された解釈が関連するような他の場合でも拡大して使われている。多くの場合、1つ以上の単純でコンパクトなコードとして報告され、この要素は、結果の意味や正常かどうかを示すために、レポートや時系列表で結果値の隣に配置されることがよくある。</t>
   </si>
   <si>
@@ -1337,6 +1351,9 @@
 </t>
   </si>
   <si>
+    <t>結果に対するコメント 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>観察（結果）に関する一般的な記述、重要な、予期しない、または信頼できない結果値に関する記述、またはその解釈に関連する場合はそのソースに関する情報が含まれる場合がある。</t>
   </si>
   <si>
@@ -1353,12 +1370,12 @@
     <t>Observation.bodySite</t>
   </si>
   <si>
-    <t>特定の歯（歯式）</t>
-  </si>
-  <si>
-    <t>優先順位は以下の番号を推奨する。
-1.FDI
-2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
+    <t>観察された身体部位 【JP Core仕様】特定の歯（歯式）を指定</t>
+  </si>
+  <si>
+    <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
+ユースケースでは、ボディサイトを個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalBodySite_VS</t>
@@ -1382,20 +1399,30 @@
     <t>Observation.bodySite.extension</t>
   </si>
   <si>
-    <t>Observation.bodySite.extension:bodyStructure</t>
-  </si>
-  <si>
-    <t>bodyStructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_BodyStructure}
+    <t>Observation.bodySite.extension:toothRoot</t>
+  </si>
+  <si>
+    <t>toothRoot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_ToothRoot}
 </t>
   </si>
   <si>
-    <t>特定の歯の歯面</t>
-  </si>
-  <si>
-    <t>特定の歯の歯面を格納するための拡張</t>
+    <t>【JP Core仕様】特定の歯の歯根を指定</t>
+  </si>
+  <si>
+    <t>Observation.bodySite.extension:toothSurface</t>
+  </si>
+  <si>
+    <t>toothSurface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_DentalOral_ToothSurface}
+</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】特定の歯の歯面を指定</t>
   </si>
   <si>
     <t>Observation.bodySite.coding</t>
@@ -1435,6 +1462,9 @@
 </t>
   </si>
   <si>
+    <t>観察（観測、検査）に使われた検体材料 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>`Observation.code`にあるコードで暗黙的に示されない場合にのみ使用する必要がある。検体自体の観察は行われない。観察（観測、検査）対象者に対して実施されるが、多くの場合には対象者から得られた検体に対して実施される。検体が奥の場合に関わるが、それらは常に追跡され、明示的に報告されるとは限らないことに注意すること。またobservationリソースは、検体を明示的に記述するような状況下（診断レポートなど）で使用される場合があることに注意。</t>
   </si>
   <si>
@@ -1457,10 +1487,10 @@
 </t>
   </si>
   <si>
+    <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
+  </si>
+  <si>
     <t>例：口腔内スキャナなど</t>
-  </si>
-  <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>
@@ -1482,6 +1512,9 @@
 </t>
   </si>
   <si>
+    <t>基準範囲との比較による結果の解釈方法のガイダンス</t>
+  </si>
+  <si>
     <t>通常の範囲または推奨範囲と比較して値を解釈する方法に関するガイダンス。複数の参照範囲は「OR」として解釈される。つまり、2つの異なるターゲット母集団を表すために、2つの `referenceRange`要素が使用される。</t>
   </si>
   <si>
@@ -1489,7 +1522,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1560,7 +1593,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
@@ -1645,7 +1678,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1668,6 +1701,9 @@
 </t>
   </si>
   <si>
+    <t>observationの発生源に関連する測定 【JP Core仕様】未使用</t>
+  </si>
+  <si>
     <t>この要素にリストされているすべての参照の選択肢は、派生値の元のデータなる可能性のある臨床観察やその他の測定値を表すことができる。最も一般的な参照先は、別のobservationである。observationをグループに一緒にまとめる方法については、以下の[メモ]（observation.html＃obsgrouping）を参照すること。</t>
   </si>
   <si>
@@ -1677,7 +1713,7 @@
     <t>Observation.component</t>
   </si>
   <si>
-    <t>特定の現存歯の処置状態</t>
+    <t>複合的な結果 【JP Core仕様】特定の現存歯の処置状態</t>
   </si>
   <si>
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
@@ -1710,8 +1746,8 @@
     <t>観察されたものについて説明します。これは、「コード」と呼ばれることがあります。 / Describes what was observed. Sometimes this is called the observation "code".</t>
   </si>
   <si>
-    <t>2つのいずれかのコードを設定する。
-主コード（primary）は、細かい粒度の現存歯の処置状態
+    <t>2つのいずれかのコードを設定する。
+主コード（primary）は、細かい粒度の現存歯の処置状態
 副コード（sub）は、粗い粒度の現存歯の処置状態</t>
   </si>
   <si>
@@ -1728,13 +1764,31 @@
     <t>Observation.component.code.coding</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
+    <t>Observation.component.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.component.code.coding.userSelected</t>
+  </si>
+  <si>
     <t>Observation.component.code.coding:primary</t>
   </si>
   <si>
@@ -1750,46 +1804,25 @@
     <t>Observation.component.code.coding:primary.id</t>
   </si>
   <si>
-    <t>Observation.component.code.coding.id</t>
-  </si>
-  <si>
     <t>Observation.component.code.coding:primary.extension</t>
   </si>
   <si>
-    <t>Observation.component.code.coding.extension</t>
-  </si>
-  <si>
     <t>Observation.component.code.coding:primary.system</t>
   </si>
   <si>
-    <t>Observation.component.code.coding.system</t>
-  </si>
-  <si>
     <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalPresentTeethObservation_CS</t>
   </si>
   <si>
     <t>Observation.component.code.coding:primary.version</t>
   </si>
   <si>
-    <t>Observation.component.code.coding.version</t>
-  </si>
-  <si>
     <t>Observation.component.code.coding:primary.code</t>
   </si>
   <si>
-    <t>Observation.component.code.coding.code</t>
-  </si>
-  <si>
     <t>Observation.component.code.coding:primary.display</t>
   </si>
   <si>
-    <t>Observation.component.code.coding.display</t>
-  </si>
-  <si>
     <t>Observation.component.code.coding:primary.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.component.code.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.component.code.coding:sub</t>
@@ -1860,7 +1893,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2195,12 +2228,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP123"/>
+  <dimension ref="A1:AP131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.19921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.1484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.87109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2222,7 +2255,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="72.98046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -3485,9 +3518,11 @@
       <c r="M11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="N11" s="2"/>
+      <c r="N11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>83</v>
@@ -3551,19 +3586,19 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>83</v>
@@ -3571,14 +3606,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3597,17 +3632,19 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>83</v>
@@ -3656,7 +3693,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3671,16 +3708,16 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>83</v>
@@ -3691,14 +3728,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3717,16 +3754,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3776,7 +3813,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3791,16 +3828,16 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>83</v>
@@ -3811,10 +3848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3840,16 +3877,16 @@
         <v>114</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>83</v>
@@ -3874,13 +3911,13 @@
         <v>83</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>83</v>
@@ -3898,7 +3935,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>94</v>
@@ -3913,19 +3950,19 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>83</v>
@@ -3933,10 +3970,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3944,7 +3981,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>82</v>
@@ -3959,19 +3996,19 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
@@ -3999,26 +4036,26 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4042,10 +4079,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -4053,13 +4090,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -4081,19 +4118,19 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -4118,11 +4155,11 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4140,7 +4177,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4164,10 +4201,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4175,10 +4212,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4201,13 +4238,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4258,7 +4295,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4282,7 +4319,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4293,10 +4330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4325,7 +4362,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4366,19 +4403,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4402,7 +4439,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4413,10 +4450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4439,19 +4476,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4500,7 +4537,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4521,10 +4558,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4535,10 +4572,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4561,13 +4598,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4618,7 +4655,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4642,7 +4679,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4653,10 +4690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4685,7 +4722,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4726,19 +4763,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4762,7 +4799,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4773,10 +4810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4802,23 +4839,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4860,7 +4897,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4881,10 +4918,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4895,10 +4932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4921,16 +4958,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4980,7 +5017,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5001,10 +5038,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5015,10 +5052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5044,21 +5081,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -5100,7 +5137,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5121,10 +5158,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5135,10 +5172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5161,17 +5198,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5181,7 +5218,7 @@
         <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>83</v>
@@ -5220,7 +5257,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5241,10 +5278,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5255,10 +5292,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5281,19 +5318,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5342,7 +5379,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5363,10 +5400,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5377,10 +5414,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5403,19 +5440,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5464,7 +5501,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5485,10 +5522,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5499,13 +5536,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5527,19 +5564,19 @@
         <v>83</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5567,10 +5604,10 @@
         <v>118</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5588,7 +5625,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5612,10 +5649,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5623,10 +5660,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5649,13 +5686,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5706,7 +5743,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5730,7 +5767,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5741,10 +5778,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5773,7 +5810,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5814,19 +5851,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5850,7 +5887,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5861,10 +5898,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5887,19 +5924,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5948,7 +5985,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5969,10 +6006,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5983,10 +6020,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6009,13 +6046,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6066,7 +6103,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6090,7 +6127,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6101,10 +6138,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6133,7 +6170,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6174,19 +6211,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6210,7 +6247,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6221,10 +6258,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6250,23 +6287,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6308,7 +6345,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6329,10 +6366,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6343,10 +6380,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6369,16 +6406,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6428,7 +6465,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6449,10 +6486,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6463,10 +6500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6492,21 +6529,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6548,7 +6585,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6569,10 +6606,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6583,10 +6620,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6609,17 +6646,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6668,7 +6705,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6689,10 +6726,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6703,10 +6740,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6729,19 +6766,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6790,7 +6827,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6811,10 +6848,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6825,10 +6862,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6851,19 +6888,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6912,7 +6949,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6933,10 +6970,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6947,13 +6984,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6975,19 +7012,19 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7012,11 +7049,11 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7034,7 +7071,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7058,10 +7095,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -7069,10 +7106,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7095,13 +7132,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7152,7 +7189,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7176,7 +7213,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7187,10 +7224,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7219,7 +7256,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7260,19 +7297,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7296,7 +7333,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7307,10 +7344,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7333,19 +7370,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7394,7 +7431,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7415,10 +7452,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7429,10 +7466,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7455,13 +7492,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7512,7 +7549,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7536,7 +7573,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7547,10 +7584,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7579,7 +7616,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7620,19 +7657,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7656,7 +7693,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7667,10 +7704,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7696,23 +7733,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7754,7 +7791,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7775,10 +7812,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7789,10 +7826,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7815,16 +7852,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7874,7 +7911,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7895,10 +7932,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7909,10 +7946,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7938,21 +7975,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7994,7 +8031,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8015,10 +8052,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8029,10 +8066,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8055,17 +8092,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8114,7 +8151,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8135,10 +8172,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8149,10 +8186,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8175,19 +8212,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8236,7 +8273,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8257,10 +8294,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8271,10 +8308,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8297,19 +8334,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8358,7 +8395,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8379,10 +8416,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8393,14 +8430,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8419,19 +8456,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8456,13 +8493,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8480,7 +8517,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8495,30 +8532,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8541,13 +8578,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8598,7 +8635,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8622,7 +8659,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8633,10 +8670,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8665,7 +8702,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8706,19 +8743,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8742,7 +8779,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8753,10 +8790,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8779,19 +8816,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8840,7 +8877,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8861,10 +8898,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8875,10 +8912,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8901,13 +8938,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8958,7 +8995,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8982,7 +9019,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8993,10 +9030,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9025,7 +9062,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -9066,19 +9103,19 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9102,7 +9139,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9113,10 +9150,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9142,23 +9179,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9200,7 +9237,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9221,10 +9258,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9235,10 +9272,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9261,16 +9298,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9320,7 +9357,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9341,10 +9378,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9355,10 +9392,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9384,21 +9421,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9440,7 +9477,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9461,10 +9498,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9475,10 +9512,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9501,17 +9538,17 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9521,7 +9558,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9560,7 +9597,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9581,10 +9618,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9595,10 +9632,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9621,19 +9658,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9682,7 +9719,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9703,10 +9740,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9717,10 +9754,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9743,19 +9780,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9804,7 +9841,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9825,10 +9862,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9839,10 +9876,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9850,7 +9887,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>94</v>
@@ -9865,19 +9902,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9926,7 +9963,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9941,19 +9978,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9961,10 +9998,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9987,16 +10024,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>162</v>
+        <v>360</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10046,7 +10083,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10067,13 +10104,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -10081,14 +10118,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10107,19 +10144,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10168,7 +10205,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10183,19 +10220,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10203,14 +10240,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10229,19 +10266,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10290,7 +10327,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10305,19 +10342,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10325,10 +10362,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10351,16 +10388,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10410,7 +10447,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10431,13 +10468,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10445,10 +10482,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10471,19 +10508,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10532,7 +10569,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10547,19 +10584,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10567,10 +10604,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10593,19 +10630,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10654,7 +10691,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10663,7 +10700,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10672,27 +10709,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10715,19 +10752,19 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10752,13 +10789,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10776,7 +10813,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10785,7 +10822,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10800,7 +10837,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10811,14 +10848,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10837,19 +10874,19 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>162</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>162</v>
+        <v>419</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10874,13 +10911,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10898,7 +10935,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10916,27 +10953,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10959,19 +10996,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11020,7 +11057,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11041,10 +11078,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11055,10 +11092,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11081,16 +11118,16 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11120,7 +11157,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -11138,7 +11175,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11156,27 +11193,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11199,13 +11236,13 @@
         <v>83</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11256,7 +11293,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11280,7 +11317,7 @@
         <v>83</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11291,10 +11328,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11323,7 +11360,7 @@
         <v>141</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11364,19 +11401,19 @@
         <v>83</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11400,7 +11437,7 @@
         <v>83</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11411,13 +11448,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>83</v>
@@ -11439,13 +11476,13 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11496,7 +11533,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11531,12 +11568,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11554,23 +11593,19 @@
         <v>83</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>218</v>
+        <v>451</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>219</v>
+        <v>452</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>83</v>
       </c>
@@ -11618,7 +11653,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11630,7 +11665,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11639,10 +11674,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11653,10 +11688,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11667,7 +11702,7 @@
         <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>83</v>
@@ -11679,19 +11714,19 @@
         <v>95</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>279</v>
+        <v>223</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>281</v>
+        <v>225</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11740,13 +11775,13 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>83</v>
@@ -11761,10 +11796,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11775,10 +11810,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11798,22 +11833,22 @@
         <v>83</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>448</v>
+        <v>280</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>448</v>
+        <v>281</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>449</v>
+        <v>282</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>450</v>
+        <v>283</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -11838,13 +11873,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -11862,7 +11897,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>447</v>
+        <v>284</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11883,10 +11918,10 @@
         <v>83</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>453</v>
+        <v>285</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>454</v>
+        <v>286</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11923,18 +11958,20 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L81" t="s" s="2">
-        <v>162</v>
-      </c>
       <c r="M81" t="s" s="2">
-        <v>162</v>
+        <v>456</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
       </c>
@@ -11958,13 +11995,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12000,27 +12037,27 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>461</v>
+        <v>83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12043,16 +12080,16 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12102,7 +12139,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12120,27 +12157,27 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12151,7 +12188,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
@@ -12163,20 +12200,18 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>83</v>
       </c>
@@ -12224,45 +12259,45 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>474</v>
+        <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>83</v>
+        <v>475</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>83</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12273,7 +12308,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>83</v>
@@ -12285,16 +12320,20 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>205</v>
+        <v>480</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>206</v>
+        <v>481</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
       </c>
@@ -12342,19 +12381,19 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>208</v>
+        <v>479</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>83</v>
+        <v>484</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>83</v>
@@ -12363,10 +12402,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>83</v>
+        <v>485</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>209</v>
+        <v>486</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12377,21 +12416,21 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>83</v>
@@ -12403,17 +12442,15 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12462,19 +12499,19 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>83</v>
@@ -12486,7 +12523,7 @@
         <v>83</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12497,14 +12534,14 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>480</v>
+        <v>139</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12517,26 +12554,24 @@
         <v>83</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>481</v>
+        <v>141</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>482</v>
+        <v>215</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O86" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>83</v>
       </c>
@@ -12584,7 +12619,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>483</v>
+        <v>218</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12608,7 +12643,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12619,42 +12654,46 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>83</v>
+        <v>490</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>485</v>
+        <v>140</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
       </c>
@@ -12702,19 +12741,19 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>488</v>
+        <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -12723,10 +12762,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>489</v>
+        <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>490</v>
+        <v>137</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12737,10 +12776,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12763,13 +12802,13 @@
         <v>83</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12820,7 +12859,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12829,7 +12868,7 @@
         <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>106</v>
@@ -12841,10 +12880,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12855,10 +12894,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12881,20 +12920,16 @@
         <v>83</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>188</v>
+        <v>495</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>83</v>
       </c>
@@ -12918,32 +12953,32 @@
         <v>83</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>500</v>
+        <v>83</v>
       </c>
       <c r="Z89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF89" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AA89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12951,7 +12986,7 @@
         <v>94</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>83</v>
+        <v>498</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>106</v>
@@ -12960,13 +12995,13 @@
         <v>83</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12977,10 +13012,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12991,7 +13026,7 @@
         <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>83</v>
@@ -13003,19 +13038,19 @@
         <v>83</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13040,13 +13075,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>324</v>
+        <v>118</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13064,13 +13099,13 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>83</v>
@@ -13082,13 +13117,13 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -13099,10 +13134,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13113,7 +13148,7 @@
         <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>83</v>
@@ -13125,17 +13160,19 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>512</v>
+        <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13160,13 +13197,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>83</v>
+        <v>519</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>83</v>
+        <v>520</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13184,13 +13221,13 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>83</v>
@@ -13202,13 +13239,13 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>83</v>
+        <v>512</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>516</v>
+        <v>426</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13219,10 +13256,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13245,16 +13282,18 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>205</v>
+        <v>522</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13302,7 +13341,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13323,10 +13362,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>489</v>
+        <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13337,10 +13376,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13351,7 +13390,7 @@
         <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>83</v>
@@ -13360,20 +13399,18 @@
         <v>83</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>522</v>
+        <v>208</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13422,13 +13459,13 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>83</v>
@@ -13443,10 +13480,10 @@
         <v>83</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13457,10 +13494,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13483,16 +13520,16 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>162</v>
+        <v>533</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>162</v>
+        <v>533</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13542,7 +13579,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13563,10 +13600,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13577,10 +13614,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13603,20 +13640,18 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>471</v>
+        <v>538</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>83</v>
       </c>
@@ -13664,7 +13699,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13688,7 +13723,7 @@
         <v>535</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -13699,10 +13734,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13713,7 +13748,7 @@
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>83</v>
@@ -13722,19 +13757,23 @@
         <v>83</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>205</v>
+        <v>480</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>206</v>
+        <v>543</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
       </c>
@@ -13782,19 +13821,19 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>208</v>
+        <v>542</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>83</v>
@@ -13803,10 +13842,10 @@
         <v>83</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>83</v>
+        <v>546</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>209</v>
+        <v>547</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13817,21 +13856,21 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>83</v>
@@ -13843,17 +13882,15 @@
         <v>83</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13902,19 +13939,19 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>83</v>
@@ -13926,7 +13963,7 @@
         <v>83</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13937,14 +13974,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>480</v>
+        <v>139</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13957,26 +13994,24 @@
         <v>83</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K98" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>481</v>
+        <v>141</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>482</v>
+        <v>215</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O98" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
@@ -14024,7 +14059,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>483</v>
+        <v>218</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14048,7 +14083,7 @@
         <v>83</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14059,45 +14094,45 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>83</v>
+        <v>490</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>541</v>
+        <v>491</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>542</v>
+        <v>492</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>543</v>
+        <v>143</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14122,13 +14157,13 @@
         <v>83</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>326</v>
+        <v>83</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>83</v>
@@ -14146,34 +14181,34 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>540</v>
+        <v>493</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>544</v>
+        <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>83</v>
@@ -14181,10 +14216,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14192,7 +14227,7 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G100" t="s" s="2">
         <v>94</v>
@@ -14204,19 +14239,23 @@
         <v>83</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>206</v>
+        <v>552</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
@@ -14240,13 +14279,13 @@
         <v>83</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>83</v>
@@ -14264,10 +14303,10 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>208</v>
+        <v>551</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>94</v>
@@ -14276,22 +14315,22 @@
         <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>83</v>
+        <v>555</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="AP100" t="s" s="2">
         <v>83</v>
@@ -14299,21 +14338,21 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>83</v>
@@ -14325,17 +14364,15 @@
         <v>83</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14372,31 +14409,31 @@
         <v>83</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>83</v>
@@ -14408,7 +14445,7 @@
         <v>83</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14419,18 +14456,18 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>548</v>
+        <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>82</v>
@@ -14442,23 +14479,21 @@
         <v>83</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>219</v>
+        <v>141</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>83</v>
       </c>
@@ -14494,17 +14529,19 @@
         <v>83</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AC102" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="AD102" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -14516,7 +14553,7 @@
         <v>83</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>83</v>
@@ -14525,10 +14562,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>224</v>
+        <v>83</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -14539,23 +14576,21 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>83</v>
@@ -14567,19 +14602,19 @@
         <v>95</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>552</v>
+        <v>222</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>552</v>
+        <v>223</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -14604,29 +14639,29 @@
         <v>83</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>553</v>
+        <v>83</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>559</v>
+      </c>
+      <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -14647,10 +14682,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -14661,10 +14696,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14687,13 +14722,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14744,7 +14779,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -14768,7 +14803,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -14779,10 +14814,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14811,7 +14846,7 @@
         <v>141</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>143</v>
@@ -14852,19 +14887,19 @@
         <v>83</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14888,7 +14923,7 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -14899,10 +14934,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14910,7 +14945,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>94</v>
@@ -14928,23 +14963,23 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>560</v>
+        <v>83</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>83</v>
@@ -14986,7 +15021,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15007,10 +15042,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15021,10 +15056,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15047,16 +15082,16 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -15106,7 +15141,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15127,10 +15162,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15141,7 +15176,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>564</v>
@@ -15170,14 +15205,14 @@
         <v>114</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
@@ -15226,7 +15261,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15247,10 +15282,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15264,7 +15299,7 @@
         <v>565</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15287,17 +15322,17 @@
         <v>95</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15346,7 +15381,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15367,10 +15402,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15381,10 +15416,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15407,19 +15442,19 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
@@ -15468,7 +15503,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15489,10 +15524,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15503,20 +15538,20 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>94</v>
@@ -15531,19 +15566,19 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -15572,7 +15607,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>83</v>
@@ -15590,7 +15625,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -15611,10 +15646,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -15625,10 +15660,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15651,13 +15686,13 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15708,7 +15743,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -15732,7 +15767,7 @@
         <v>83</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -15743,10 +15778,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15775,7 +15810,7 @@
         <v>141</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>143</v>
@@ -15816,19 +15851,19 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -15852,7 +15887,7 @@
         <v>83</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
@@ -15863,10 +15898,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15892,23 +15927,23 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>83</v>
@@ -15950,7 +15985,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -15971,10 +16006,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -15985,10 +16020,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16011,16 +16046,16 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16070,7 +16105,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16091,10 +16126,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16105,7 +16140,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>564</v>
@@ -16116,7 +16151,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>94</v>
@@ -16134,14 +16169,14 @@
         <v>114</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>83</v>
@@ -16190,7 +16225,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16211,10 +16246,10 @@
         <v>83</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16225,10 +16260,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16251,17 +16286,17 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>83</v>
@@ -16310,7 +16345,7 @@
         <v>83</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16331,10 +16366,10 @@
         <v>83</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16345,10 +16380,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16371,19 +16406,19 @@
         <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16432,7 +16467,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16453,10 +16488,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16467,12 +16502,14 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>83</v>
       </c>
@@ -16493,19 +16530,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>278</v>
+        <v>581</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>279</v>
+        <v>581</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>281</v>
+        <v>225</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
@@ -16530,13 +16567,11 @@
         <v>83</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>83</v>
+        <v>582</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -16554,13 +16589,13 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>83</v>
@@ -16575,10 +16610,10 @@
         <v>83</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -16589,10 +16624,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16612,23 +16647,19 @@
         <v>83</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>583</v>
+        <v>208</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>584</v>
+        <v>209</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>83</v>
       </c>
@@ -16676,7 +16707,7 @@
         <v>83</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>582</v>
+        <v>211</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -16688,44 +16719,44 @@
         <v>83</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>587</v>
+        <v>83</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>403</v>
+        <v>212</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>404</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>83</v>
@@ -16737,20 +16768,18 @@
         <v>83</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>589</v>
+        <v>141</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>590</v>
+        <v>215</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="O121" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>83</v>
       </c>
@@ -16774,43 +16803,43 @@
         <v>83</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>83</v>
+        <v>216</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>83</v>
+        <v>198</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>588</v>
+        <v>218</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>412</v>
+        <v>83</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>83</v>
@@ -16819,10 +16848,10 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>413</v>
+        <v>212</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -16833,21 +16862,21 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>592</v>
+        <v>562</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>83</v>
@@ -16856,29 +16885,29 @@
         <v>83</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>188</v>
+        <v>108</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>593</v>
+        <v>235</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>594</v>
+        <v>236</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>595</v>
+        <v>237</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>596</v>
+        <v>238</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>83</v>
+        <v>586</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>83</v>
@@ -16896,13 +16925,13 @@
         <v>83</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -16920,13 +16949,13 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>592</v>
+        <v>240</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>83</v>
@@ -16938,27 +16967,27 @@
         <v>83</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>420</v>
+        <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>421</v>
+        <v>241</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>422</v>
+        <v>242</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>423</v>
+        <v>83</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>597</v>
+        <v>563</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16969,7 +16998,7 @@
         <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>83</v>
@@ -16978,23 +17007,21 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>598</v>
+        <v>245</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>599</v>
+        <v>246</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>83</v>
       </c>
@@ -17042,13 +17069,13 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>597</v>
+        <v>248</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>83</v>
@@ -17063,15 +17090,987 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>475</v>
+        <v>249</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>476</v>
+        <v>250</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP123" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP124" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AO125" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP125" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO126" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP126" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="P127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN127" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AO127" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP127" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP128" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP129" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP130" t="s" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP131" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -2231,15 +2231,15 @@
   <dimension ref="A1:AP131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.19921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.87109375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.32421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.64453125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2250,28 +2250,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.98046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.5703125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>94</v>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-24</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -630,7 +630,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1032,7 +1032,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1127,7 +1127,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1300,7 +1300,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1329,7 +1329,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1446,7 +1446,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1483,7 +1483,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1558,7 +1558,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1608,7 +1608,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1641,7 +1641,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-dentaloral-toothtreatmentcondition.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
